--- a/temp_doc/MAPEL - TJKT.xlsx
+++ b/temp_doc/MAPEL - TJKT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5168BA36-6D78-9E42-88A7-3E127A4A2A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1482EE-C239-0D4F-8E21-392E28372B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>id_mapel</t>
   </si>
@@ -47,95 +47,209 @@
     <t>nama_mapel</t>
   </si>
   <si>
-    <t>BAHASA INDONESIA ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>PEND. PANCASILA DAN KEWARGANEGARAAN ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>PRODUK KREATIF DAN KEWIRAUSAHAAN ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII TJKT 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>PEND. PANCASILA DAN KEWARGANEGARAAN ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>PRODUK KREATIF DAN KEWIRAUSAHAAN ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII TJKT 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>PEND. PANCASILA DAN KEWARGANEGARAAN ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>PRODUK KREATIF DAN KEWIRAUSAHAAN ( XII TJKT 3 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII TJKT 3 )</t>
+    <t>AGAMA ISLAM ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X TJKT 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X TJKT 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X TJKT 3 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X TJKT 4 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>MATA PELAJARAN PILIHAN ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PJOK ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>PKK ( XI TJKT 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>MATA PELAJARAN PILIHAN ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PJOK ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>PKK ( XI TJKT 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>MATA PELAJARAN PILIHAN ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PJOK ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( XI TJKT 3 )</t>
+  </si>
+  <si>
+    <t>PKK ( XI TJKT 3 )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF858796"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +274,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -515,287 +629,709 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1025</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>10012467</v>
+      </c>
+      <c r="B2">
+        <v>1006</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>10027991</v>
+      </c>
+      <c r="B3">
+        <v>1006</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>10031269</v>
+      </c>
+      <c r="B4">
+        <v>1006</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>10046180</v>
+      </c>
+      <c r="B5">
+        <v>1006</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>10054381</v>
+      </c>
+      <c r="B6">
+        <v>1006</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>10064975</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>10075578</v>
+      </c>
+      <c r="B8">
+        <v>1006</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>10089784</v>
+      </c>
+      <c r="B9">
+        <v>1006</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>10093087</v>
+      </c>
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10104796</v>
+      </c>
+      <c r="B11">
         <v>1006</v>
       </c>
-      <c r="B7" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>10112552</v>
+      </c>
+      <c r="B12">
         <v>1007</v>
       </c>
-      <c r="B8" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>10127211</v>
+      </c>
+      <c r="B13">
+        <v>1007</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>10135509</v>
+      </c>
+      <c r="B14">
+        <v>1007</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>10143935</v>
+      </c>
+      <c r="B15">
+        <v>1007</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>10152400</v>
+      </c>
+      <c r="B16">
+        <v>1007</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>10161499</v>
+      </c>
+      <c r="B17">
+        <v>1007</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>10174183</v>
+      </c>
+      <c r="B18">
+        <v>1007</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>10184561</v>
+      </c>
+      <c r="B19">
+        <v>1007</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>10194127</v>
+      </c>
+      <c r="B20">
+        <v>1007</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>10209985</v>
+      </c>
+      <c r="B21">
+        <v>1007</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>10214298</v>
+      </c>
+      <c r="B22">
         <v>1008</v>
       </c>
-      <c r="B9" s="1">
-        <v>1025</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1013</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1014</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1015</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1016</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>1017</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1027</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>1018</v>
-      </c>
-      <c r="B19" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>1019</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>1020</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>1021</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>1022</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1026</v>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>10228116</v>
+      </c>
+      <c r="B23">
+        <v>1008</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>1023</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1026</v>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>10232410</v>
+      </c>
+      <c r="B24">
+        <v>1008</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>1024</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1026</v>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>10244517</v>
+      </c>
+      <c r="B25">
+        <v>1008</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>10256819</v>
+      </c>
+      <c r="B26">
+        <v>1008</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>10267721</v>
+      </c>
+      <c r="B27">
+        <v>1008</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>10278449</v>
+      </c>
+      <c r="B28">
+        <v>1008</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>10287232</v>
+      </c>
+      <c r="B29">
+        <v>1008</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>10294337</v>
+      </c>
+      <c r="B30">
+        <v>1008</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>10307611</v>
+      </c>
+      <c r="B31">
+        <v>1008</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>10318261</v>
+      </c>
+      <c r="B32">
+        <v>1009</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>10321189</v>
+      </c>
+      <c r="B33">
+        <v>1009</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>10333236</v>
+      </c>
+      <c r="B34">
+        <v>1009</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>10344335</v>
+      </c>
+      <c r="B35">
+        <v>1009</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>10356200</v>
+      </c>
+      <c r="B36">
+        <v>1009</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>10365602</v>
+      </c>
+      <c r="B37">
+        <v>1009</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>10375587</v>
+      </c>
+      <c r="B38">
+        <v>1009</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>10383240</v>
+      </c>
+      <c r="B39">
+        <v>1009</v>
+      </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>10393135</v>
+      </c>
+      <c r="B40">
+        <v>1009</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>10409837</v>
+      </c>
+      <c r="B41">
+        <v>1009</v>
+      </c>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>10418279</v>
+      </c>
+      <c r="B42">
+        <v>1016</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>10424965</v>
+      </c>
+      <c r="B43">
+        <v>1016</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>10434066</v>
+      </c>
+      <c r="B44">
+        <v>1016</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>10448850</v>
+      </c>
+      <c r="B45">
+        <v>1016</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>10459934</v>
+      </c>
+      <c r="B46">
+        <v>1016</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>10467600</v>
+      </c>
+      <c r="B47">
+        <v>1016</v>
+      </c>
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>10475317</v>
+      </c>
+      <c r="B48">
+        <v>1016</v>
+      </c>
+      <c r="C48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>10489174</v>
+      </c>
+      <c r="B49">
+        <v>1016</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>10498483</v>
+      </c>
+      <c r="B50">
+        <v>1017</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>10502000</v>
+      </c>
+      <c r="B51">
+        <v>1017</v>
+      </c>
+      <c r="C51" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>10519917</v>
+      </c>
+      <c r="B52">
+        <v>1017</v>
+      </c>
+      <c r="C52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>10528295</v>
+      </c>
+      <c r="B53">
+        <v>1017</v>
+      </c>
+      <c r="C53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>10537496</v>
+      </c>
+      <c r="B54">
+        <v>1017</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>10549718</v>
+      </c>
+      <c r="B55">
+        <v>1017</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>10559595</v>
+      </c>
+      <c r="B56">
+        <v>1017</v>
+      </c>
+      <c r="C56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>10561970</v>
+      </c>
+      <c r="B57">
+        <v>1017</v>
+      </c>
+      <c r="C57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>10579279</v>
+      </c>
+      <c r="B58">
+        <v>1018</v>
+      </c>
+      <c r="C58" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>10584514</v>
+      </c>
+      <c r="B59">
+        <v>1018</v>
+      </c>
+      <c r="C59" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>10591215</v>
+      </c>
+      <c r="B60">
+        <v>1018</v>
+      </c>
+      <c r="C60" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>10608461</v>
+      </c>
+      <c r="B61">
+        <v>1018</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>10618572</v>
+      </c>
+      <c r="B62">
+        <v>1018</v>
+      </c>
+      <c r="C62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>10623333</v>
+      </c>
+      <c r="B63">
+        <v>1018</v>
+      </c>
+      <c r="C63" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>10633771</v>
+      </c>
+      <c r="B64">
+        <v>1018</v>
+      </c>
+      <c r="C64" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>10649567</v>
+      </c>
+      <c r="B65">
+        <v>1018</v>
+      </c>
+      <c r="C65" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
